--- a/election_results.xlsx
+++ b/election_results.xlsx
@@ -445,7 +445,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/election_results.xlsx
+++ b/election_results.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C2"/>
+  <dimension ref="A1:C4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -445,7 +445,37 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>SNR BOYS' PREFECT</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>PREFECT TWO</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>SNR BOYS' PREFECT</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>FREDERICK APPEADU</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/election_results.xlsx
+++ b/election_results.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C4"/>
+  <dimension ref="A1:C13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -436,7 +436,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>SNR BOYS' PREFECT</t>
+          <t>BOYS' SENIOR PREFECT</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -445,37 +445,172 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>SNR BOYS' PREFECT</t>
+          <t>BOYS' SENIOR PREFECT</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>PREFECT TWO</t>
+          <t>PREFEFECT TWO</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>SNR BOYS' PREFECT</t>
+          <t>GIRLS' SENIOR PREFECT</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>FREDERICK APPEADU</t>
+          <t>PREFEFECT ONE</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0</v>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>GIRLS' SENIOR PREFECT</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>PREFEFECT TWO</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>HOUSE 1 - BOYS</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>PREFEFECT 1</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>HOUSE 1 - GIRLS</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>PREFEFECT ONE</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>HOUSE 2 - BOYS</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>PREFEFECT ONE</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>HOUSE 2 - GIRLS</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>PREFEFECT ONE</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>HOUSE 3 - BOYS</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>PREFEFECT ONE</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>HOUSE 3 - GIRLS</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>PREFEFECT ONE</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>HOUSE 4 - BOYS</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>PREFEFECT ONE</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>HOUSE 4 - GIRLS</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>PREFEFECT ONE</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
